--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/NEW_HAMPSHIRE_2021.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/NEW_HAMPSHIRE_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Comala</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -555,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -643,7 +703,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -690,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -703,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -716,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -736,7 +816,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C26">
@@ -747,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -760,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -773,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -786,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -799,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C31">
@@ -812,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -869,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C36">
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -902,7 +1032,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C38">
@@ -913,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C39">
@@ -926,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -939,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C41">
@@ -952,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Huejúcar</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Teuchitlán</t>
@@ -991,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C45">
@@ -1004,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1035,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1061,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1118,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1131,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C55">
@@ -1144,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1164,7 +1374,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C57">
@@ -1175,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>San Agustín Etla</t>
@@ -1188,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>San Juan Chilateca</t>
@@ -1201,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1232,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -1245,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1258,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -1271,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -1284,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -1297,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1328,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C69">
@@ -1341,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C70">
@@ -1354,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Pedro Escobedo</t>
@@ -1367,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1376,10 +1651,15 @@
         <v>13</v>
       </c>
       <c r="D72">
-        <v>0.09352517985611511</v>
+        <v>0.09352517985611512</v>
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1411,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -1424,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -1437,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -1450,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -1463,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1494,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -1507,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1538,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1569,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>González</t>
@@ -1582,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1613,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -1626,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -1639,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1670,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -1683,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1706,41 +2061,6 @@
       </c>
       <c r="D95">
         <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
